--- a/jogos_2026-09-30.xlsx
+++ b/jogos_2026-09-30.xlsx
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G3">
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="G4">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G9">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>JS El Biar</t>
         </is>
       </c>
       <c r="G10">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G11">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Temouchent</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G12">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>US Biskra</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G13">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Temouchent</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G14">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>JS El Biar</t>
+          <t>US Biskra</t>
         </is>
       </c>
       <c r="G15">

--- a/jogos_2026-09-30.xlsx
+++ b/jogos_2026-09-30.xlsx
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>JS El Biar</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G10">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G11">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>JS El Biar</t>
         </is>
       </c>
       <c r="G12">

--- a/jogos_2026-09-30.xlsx
+++ b/jogos_2026-09-30.xlsx
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G9">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>JS El Biar</t>
         </is>
       </c>
       <c r="G10">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Temouchent</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G11">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>JS El Biar</t>
+          <t>US Biskra</t>
         </is>
       </c>
       <c r="G12">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G13">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Temouchent</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G14">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>US Biskra</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G15">

--- a/jogos_2026-09-30.xlsx
+++ b/jogos_2026-09-30.xlsx
@@ -1772,7 +1772,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N9">
@@ -2098,7 +2098,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N11">
@@ -2587,7 +2587,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N14">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N15">

--- a/jogos_2026-09-30.xlsx
+++ b/jogos_2026-09-30.xlsx
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G14">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G15">

--- a/jogos_2026-09-30.xlsx
+++ b/jogos_2026-09-30.xlsx
@@ -1609,7 +1609,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N8">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N10">
@@ -2261,7 +2261,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N12">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N13">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G14">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G15">

--- a/jogos_2026-09-30.xlsx
+++ b/jogos_2026-09-30.xlsx
@@ -2261,7 +2261,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N12">

--- a/jogos_2026-09-30.xlsx
+++ b/jogos_2026-09-30.xlsx
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Temouchent</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>JS El Biar</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G10">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Temouchent</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>US Biskra</t>
         </is>
       </c>
       <c r="G11">
@@ -2098,7 +2098,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N11">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>US Biskra</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G12">
@@ -2261,7 +2261,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N12">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G13">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G14">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>JS El Biar</t>
         </is>
       </c>
       <c r="G15">

--- a/jogos_2026-09-30.xlsx
+++ b/jogos_2026-09-30.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU16"/>
+  <dimension ref="A1:AU17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>4.58</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="G7">
@@ -1446,68 +1446,68 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X7">
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>6.41</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>2026-09-30 21:00:00</t>
+          <t>2026-09-30 20:30:00</t>
         </is>
       </c>
     </row>
@@ -1571,22 +1571,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G8">
@@ -1609,68 +1609,68 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G9">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Temouchent</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G10">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G12">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G13">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G14">
@@ -2870,156 +2870,319 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Algeria Ligue 1</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Temouchent</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>ASO Chlef</t>
+        </is>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>suspended</t>
+        </is>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>0</v>
+      </c>
+      <c r="Q16">
+        <v>0</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>0</v>
+      </c>
+      <c r="U16">
+        <v>0</v>
+      </c>
+      <c r="V16">
+        <v>0</v>
+      </c>
+      <c r="W16">
+        <v>0</v>
+      </c>
+      <c r="X16">
+        <v>0</v>
+      </c>
+      <c r="Y16">
+        <v>0</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+      <c r="AA16">
+        <v>0</v>
+      </c>
+      <c r="AB16">
+        <v>0</v>
+      </c>
+      <c r="AC16">
+        <v>0</v>
+      </c>
+      <c r="AD16">
+        <v>0</v>
+      </c>
+      <c r="AE16">
+        <v>0</v>
+      </c>
+      <c r="AF16">
+        <v>0</v>
+      </c>
+      <c r="AG16">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ16">
+        <v>0</v>
+      </c>
+      <c r="AK16">
+        <v>0</v>
+      </c>
+      <c r="AL16">
+        <v>0</v>
+      </c>
+      <c r="AM16">
+        <v>-1</v>
+      </c>
+      <c r="AN16">
+        <v>-1</v>
+      </c>
+      <c r="AO16">
+        <v>-1</v>
+      </c>
+      <c r="AP16">
+        <v>-1</v>
+      </c>
+      <c r="AQ16">
+        <v>0</v>
+      </c>
+      <c r="AR16">
+        <v>0</v>
+      </c>
+      <c r="AS16">
+        <v>0</v>
+      </c>
+      <c r="AT16">
+        <v>0</v>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>2026-09-30 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
           <t>23:00</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>USA USL Championship</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>Sacramento Republic</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>Las Vegas Lights</t>
         </is>
       </c>
-      <c r="G16">
-        <v>0</v>
-      </c>
-      <c r="H16">
-        <v>0</v>
-      </c>
-      <c r="I16">
-        <v>0</v>
-      </c>
-      <c r="J16">
-        <v>0</v>
-      </c>
-      <c r="K16">
-        <v>0</v>
-      </c>
-      <c r="L16">
-        <v>0</v>
-      </c>
-      <c r="M16" t="inlineStr">
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N16">
-        <v>0</v>
-      </c>
-      <c r="O16">
-        <v>0</v>
-      </c>
-      <c r="P16">
-        <v>0</v>
-      </c>
-      <c r="Q16">
-        <v>0</v>
-      </c>
-      <c r="R16">
-        <v>0</v>
-      </c>
-      <c r="S16">
-        <v>0</v>
-      </c>
-      <c r="T16">
-        <v>0</v>
-      </c>
-      <c r="U16">
-        <v>0</v>
-      </c>
-      <c r="V16">
-        <v>0</v>
-      </c>
-      <c r="W16">
-        <v>0</v>
-      </c>
-      <c r="X16">
-        <v>0</v>
-      </c>
-      <c r="Y16">
-        <v>0</v>
-      </c>
-      <c r="Z16">
-        <v>0</v>
-      </c>
-      <c r="AA16">
-        <v>0</v>
-      </c>
-      <c r="AB16">
-        <v>0</v>
-      </c>
-      <c r="AC16">
-        <v>0</v>
-      </c>
-      <c r="AD16">
-        <v>0</v>
-      </c>
-      <c r="AE16">
-        <v>0</v>
-      </c>
-      <c r="AF16">
-        <v>0</v>
-      </c>
-      <c r="AG16">
-        <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr">
+      <c r="N17">
+        <v>1.58</v>
+      </c>
+      <c r="O17">
+        <v>3.95</v>
+      </c>
+      <c r="P17">
+        <v>5.2</v>
+      </c>
+      <c r="Q17">
+        <v>2.08</v>
+      </c>
+      <c r="R17">
+        <v>2.21</v>
+      </c>
+      <c r="S17">
+        <v>1.3</v>
+      </c>
+      <c r="T17">
+        <v>3</v>
+      </c>
+      <c r="U17">
+        <v>2.51</v>
+      </c>
+      <c r="V17">
+        <v>1.42</v>
+      </c>
+      <c r="W17">
+        <v>1.07</v>
+      </c>
+      <c r="X17">
+        <v>1</v>
+      </c>
+      <c r="Y17">
+        <v>1.22</v>
+      </c>
+      <c r="Z17">
+        <v>3.48</v>
+      </c>
+      <c r="AA17">
+        <v>1.82</v>
+      </c>
+      <c r="AB17">
+        <v>1.85</v>
+      </c>
+      <c r="AC17">
+        <v>3.08</v>
+      </c>
+      <c r="AD17">
+        <v>1.28</v>
+      </c>
+      <c r="AE17">
+        <v>1.06</v>
+      </c>
+      <c r="AF17">
+        <v>1.86</v>
+      </c>
+      <c r="AG17">
+        <v>1.83</v>
+      </c>
+      <c r="AH17" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI16" t="inlineStr">
+      <c r="AI17" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AJ16">
-        <v>0</v>
-      </c>
-      <c r="AK16">
-        <v>0</v>
-      </c>
-      <c r="AL16">
-        <v>0</v>
-      </c>
-      <c r="AM16">
-        <v>-1</v>
-      </c>
-      <c r="AN16">
-        <v>-1</v>
-      </c>
-      <c r="AO16">
-        <v>-1</v>
-      </c>
-      <c r="AP16">
-        <v>-1</v>
-      </c>
-      <c r="AQ16">
-        <v>0</v>
-      </c>
-      <c r="AR16">
-        <v>0</v>
-      </c>
-      <c r="AS16">
-        <v>0</v>
-      </c>
-      <c r="AT16">
-        <v>0</v>
-      </c>
-      <c r="AU16" t="inlineStr">
+      <c r="AJ17">
+        <v>1.17</v>
+      </c>
+      <c r="AK17">
+        <v>2.24</v>
+      </c>
+      <c r="AL17">
+        <v>0</v>
+      </c>
+      <c r="AM17">
+        <v>-1</v>
+      </c>
+      <c r="AN17">
+        <v>-1</v>
+      </c>
+      <c r="AO17">
+        <v>-1</v>
+      </c>
+      <c r="AP17">
+        <v>-1</v>
+      </c>
+      <c r="AQ17">
+        <v>0</v>
+      </c>
+      <c r="AR17">
+        <v>0</v>
+      </c>
+      <c r="AS17">
+        <v>0</v>
+      </c>
+      <c r="AT17">
+        <v>0</v>
+      </c>
+      <c r="AU17" t="inlineStr">
         <is>
           <t>2026-09-30 23:00:00</t>
         </is>

--- a/jogos_2026-09-30.xlsx
+++ b/jogos_2026-09-30.xlsx
@@ -798,10 +798,10 @@
         </is>
       </c>
       <c r="N3">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="O3">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="P3">
         <v>1.92</v>
@@ -843,10 +843,10 @@
         <v>1.76</v>
       </c>
       <c r="AC3">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="AD3">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE3">
         <v>1.06</v>
@@ -961,16 +961,16 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="O4">
         <v>3.65</v>
       </c>
       <c r="P4">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="Q4">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="R4">
         <v>2.14</v>
@@ -988,7 +988,7 @@
         <v>1.59</v>
       </c>
       <c r="W4">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X4">
         <v>1.01</v>
@@ -997,7 +997,7 @@
         <v>1.13</v>
       </c>
       <c r="Z4">
-        <v>4.6</v>
+        <v>4.92</v>
       </c>
       <c r="AA4">
         <v>1.51</v>
@@ -1015,10 +1015,10 @@
         <v>1.19</v>
       </c>
       <c r="AF4">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="AG4">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>1.22</v>
       </c>
       <c r="AK4">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1287,19 +1287,19 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="O6">
         <v>3.75</v>
       </c>
       <c r="P6">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="Q6">
-        <v>2.23</v>
+        <v>2.18</v>
       </c>
       <c r="R6">
-        <v>2.22</v>
+        <v>2.39</v>
       </c>
       <c r="S6">
         <v>1.28</v>
@@ -1317,16 +1317,16 @@
         <v>1.06</v>
       </c>
       <c r="X6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y6">
         <v>1.19</v>
       </c>
       <c r="Z6">
-        <v>3.78</v>
+        <v>3.8</v>
       </c>
       <c r="AA6">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AB6">
         <v>2.01</v>
@@ -1360,7 +1360,7 @@
         <v>1.13</v>
       </c>
       <c r="AK6">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1622,19 +1622,19 @@
         <v>3.6</v>
       </c>
       <c r="Q8">
-        <v>2.47</v>
+        <v>2.39</v>
       </c>
       <c r="R8">
-        <v>2.19</v>
+        <v>2.35</v>
       </c>
       <c r="S8">
         <v>1.3</v>
       </c>
       <c r="T8">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="U8">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="V8">
         <v>1.46</v>
@@ -1649,13 +1649,13 @@
         <v>1.24</v>
       </c>
       <c r="Z8">
-        <v>3.82</v>
+        <v>3.84</v>
       </c>
       <c r="AA8">
         <v>1.76</v>
       </c>
       <c r="AB8">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="AC8">
         <v>2.83</v>
@@ -1667,10 +1667,10 @@
         <v>1.09</v>
       </c>
       <c r="AF8">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AG8">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK8">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="O17">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="P17">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="Q17">
         <v>2.08</v>
@@ -3150,7 +3150,7 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AK17">
         <v>2.24</v>

--- a/jogos_2026-09-30.xlsx
+++ b/jogos_2026-09-30.xlsx
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="N7">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="O7">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="P7">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="Q7">
         <v>3.57</v>
@@ -1772,7 +1772,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N9">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N10">
@@ -2261,7 +2261,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N12">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N13">
@@ -2587,7 +2587,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N14">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N15">
@@ -2913,7 +2913,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N16">

--- a/jogos_2026-09-30.xlsx
+++ b/jogos_2026-09-30.xlsx
@@ -810,7 +810,7 @@
         <v>4.58</v>
       </c>
       <c r="R3">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="S3">
         <v>1.36</v>
@@ -819,13 +819,13 @@
         <v>2.72</v>
       </c>
       <c r="U3">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="V3">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W3">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X3">
         <v>1.01</v>
@@ -837,10 +837,10 @@
         <v>3.08</v>
       </c>
       <c r="AA3">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AB3">
-        <v>1.76</v>
+        <v>1.87</v>
       </c>
       <c r="AC3">
         <v>3.2</v>
@@ -868,7 +868,7 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.76</v>
+        <v>1.22</v>
       </c>
       <c r="AK3">
         <v>1.18</v>
@@ -970,10 +970,10 @@
         <v>4</v>
       </c>
       <c r="Q4">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="R4">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="S4">
         <v>1.27</v>
@@ -988,19 +988,19 @@
         <v>1.59</v>
       </c>
       <c r="W4">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X4">
         <v>1.01</v>
       </c>
       <c r="Y4">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="Z4">
-        <v>4.92</v>
+        <v>4.89</v>
       </c>
       <c r="AA4">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AB4">
         <v>2.26</v>
@@ -1015,7 +1015,7 @@
         <v>1.19</v>
       </c>
       <c r="AF4">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AG4">
         <v>2.3</v>
@@ -1034,7 +1034,7 @@
         <v>1.22</v>
       </c>
       <c r="AK4">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -1296,10 +1296,10 @@
         <v>4.1</v>
       </c>
       <c r="Q6">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="R6">
-        <v>2.39</v>
+        <v>2.23</v>
       </c>
       <c r="S6">
         <v>1.28</v>
@@ -1323,13 +1323,13 @@
         <v>1.19</v>
       </c>
       <c r="Z6">
-        <v>3.8</v>
+        <v>3.78</v>
       </c>
       <c r="AA6">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AB6">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="AC6">
         <v>2.83</v>
@@ -1625,7 +1625,7 @@
         <v>2.39</v>
       </c>
       <c r="R8">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="S8">
         <v>1.3</v>
@@ -1652,13 +1652,13 @@
         <v>3.84</v>
       </c>
       <c r="AA8">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="AB8">
-        <v>2.03</v>
+        <v>1.96</v>
       </c>
       <c r="AC8">
-        <v>2.83</v>
+        <v>2.81</v>
       </c>
       <c r="AD8">
         <v>1.33</v>
@@ -1667,10 +1667,10 @@
         <v>1.09</v>
       </c>
       <c r="AF8">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AG8">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -3083,7 +3083,7 @@
         <v>1.55</v>
       </c>
       <c r="O17">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="P17">
         <v>5.4</v>
@@ -3101,28 +3101,28 @@
         <v>3</v>
       </c>
       <c r="U17">
-        <v>2.51</v>
+        <v>2.55</v>
       </c>
       <c r="V17">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W17">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X17">
         <v>1</v>
       </c>
       <c r="Y17">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z17">
-        <v>3.48</v>
+        <v>3.42</v>
       </c>
       <c r="AA17">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AB17">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AC17">
         <v>3.08</v>

--- a/jogos_2026-09-30.xlsx
+++ b/jogos_2026-09-30.xlsx
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="N5">
-        <v>4.3</v>
+        <v>4.25</v>
       </c>
       <c r="O5">
-        <v>3.75</v>
+        <v>3.68</v>
       </c>
       <c r="P5">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -1163,10 +1163,10 @@
         <v>0</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC5">
         <v>0</v>

--- a/jogos_2026-09-30.xlsx
+++ b/jogos_2026-09-30.xlsx
@@ -798,28 +798,28 @@
         </is>
       </c>
       <c r="N3">
-        <v>3.6</v>
+        <v>2.98</v>
       </c>
       <c r="O3">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P3">
-        <v>1.92</v>
+        <v>2.19</v>
       </c>
       <c r="Q3">
-        <v>4.58</v>
+        <v>3.88</v>
       </c>
       <c r="R3">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="S3">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="T3">
+        <v>2.88</v>
+      </c>
+      <c r="U3">
         <v>2.72</v>
-      </c>
-      <c r="U3">
-        <v>2.8</v>
       </c>
       <c r="V3">
         <v>1.36</v>
@@ -831,31 +831,31 @@
         <v>1.01</v>
       </c>
       <c r="Y3">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z3">
         <v>3.08</v>
       </c>
       <c r="AA3">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AB3">
-        <v>1.87</v>
+        <v>1.76</v>
       </c>
       <c r="AC3">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="AD3">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AE3">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF3">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AG3">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.22</v>
+        <v>1.6</v>
       </c>
       <c r="AK3">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.68</v>
+        <v>1.52</v>
       </c>
       <c r="O4">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="P4">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="Q4">
         <v>2.22</v>
       </c>
       <c r="R4">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="S4">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="T4">
-        <v>3.18</v>
+        <v>3.75</v>
       </c>
       <c r="U4">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="V4">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="W4">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X4">
         <v>1.01</v>
       </c>
       <c r="Y4">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="Z4">
-        <v>4.89</v>
+        <v>5.37</v>
       </c>
       <c r="AA4">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AB4">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="AC4">
-        <v>2.22</v>
+        <v>2.13</v>
       </c>
       <c r="AD4">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="AE4">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AF4">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AG4">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK4">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.69</v>
+        <v>1.94</v>
       </c>
       <c r="O6">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="P6">
-        <v>4.1</v>
+        <v>3.2</v>
       </c>
       <c r="Q6">
-        <v>2.22</v>
+        <v>2.32</v>
       </c>
       <c r="R6">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="S6">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T6">
-        <v>3.08</v>
+        <v>3.24</v>
       </c>
       <c r="U6">
-        <v>2.51</v>
+        <v>2.34</v>
       </c>
       <c r="V6">
-        <v>1.42</v>
+        <v>1.52</v>
       </c>
       <c r="W6">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="X6">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y6">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z6">
-        <v>3.78</v>
+        <v>4.25</v>
       </c>
       <c r="AA6">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AB6">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AC6">
-        <v>2.83</v>
+        <v>2.63</v>
       </c>
       <c r="AD6">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AE6">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF6">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AG6">
-        <v>2.01</v>
+        <v>2.25</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AK6">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1613,25 +1613,25 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.91</v>
+        <v>1.99</v>
       </c>
       <c r="O8">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P8">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="Q8">
-        <v>2.39</v>
+        <v>2.46</v>
       </c>
       <c r="R8">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="S8">
         <v>1.3</v>
       </c>
       <c r="T8">
-        <v>3.2</v>
+        <v>3.26</v>
       </c>
       <c r="U8">
         <v>2.61</v>
@@ -1646,31 +1646,31 @@
         <v>1.03</v>
       </c>
       <c r="Y8">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="Z8">
-        <v>3.84</v>
+        <v>3.82</v>
       </c>
       <c r="AA8">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AB8">
-        <v>1.96</v>
+        <v>2.05</v>
       </c>
       <c r="AC8">
         <v>2.81</v>
       </c>
       <c r="AD8">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AE8">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AF8">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AG8">
-        <v>2.09</v>
+        <v>2.14</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>1.22</v>
       </c>
       <c r="AK8">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -3080,19 +3080,19 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.55</v>
+        <v>1.43</v>
       </c>
       <c r="O17">
-        <v>3.75</v>
+        <v>3.72</v>
       </c>
       <c r="P17">
-        <v>5.4</v>
+        <v>4.75</v>
       </c>
       <c r="Q17">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="R17">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="S17">
         <v>1.3</v>
@@ -3104,10 +3104,10 @@
         <v>2.55</v>
       </c>
       <c r="V17">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W17">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X17">
         <v>1</v>
@@ -3119,25 +3119,25 @@
         <v>3.42</v>
       </c>
       <c r="AA17">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AB17">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AC17">
         <v>3.08</v>
       </c>
       <c r="AD17">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AE17">
         <v>1.06</v>
       </c>
       <c r="AF17">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="AG17">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AK17">
-        <v>2.24</v>
+        <v>2.12</v>
       </c>
       <c r="AL17">
         <v>0</v>

--- a/jogos_2026-09-30.xlsx
+++ b/jogos_2026-09-30.xlsx
@@ -1459,55 +1459,55 @@
         <v>1.85</v>
       </c>
       <c r="Q7">
-        <v>3.57</v>
+        <v>3.24</v>
       </c>
       <c r="R7">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="S7">
+        <v>1.17</v>
+      </c>
+      <c r="T7">
+        <v>4.2</v>
+      </c>
+      <c r="U7">
+        <v>2.05</v>
+      </c>
+      <c r="V7">
+        <v>1.77</v>
+      </c>
+      <c r="W7">
         <v>1.2</v>
       </c>
-      <c r="T7">
-        <v>4</v>
-      </c>
-      <c r="U7">
-        <v>2.04</v>
-      </c>
-      <c r="V7">
-        <v>1.8</v>
-      </c>
-      <c r="W7">
-        <v>1.18</v>
-      </c>
       <c r="X7">
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Z7">
-        <v>6.41</v>
+        <v>7</v>
       </c>
       <c r="AA7">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AB7">
-        <v>2.89</v>
+        <v>3</v>
       </c>
       <c r="AC7">
-        <v>2.09</v>
+        <v>1.9</v>
       </c>
       <c r="AD7">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AE7">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AF7">
         <v>1.4</v>
       </c>
       <c r="AG7">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>1.22</v>
       </c>
       <c r="AK7">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AL7">
         <v>0</v>

--- a/jogos_2026-09-30.xlsx
+++ b/jogos_2026-09-30.xlsx
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="G3">
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.98</v>
+        <v>1.52</v>
       </c>
       <c r="O3">
-        <v>3.35</v>
+        <v>4</v>
       </c>
       <c r="P3">
-        <v>2.19</v>
+        <v>3.75</v>
       </c>
       <c r="Q3">
-        <v>3.88</v>
+        <v>2.22</v>
       </c>
       <c r="R3">
-        <v>2.17</v>
+        <v>2.21</v>
       </c>
       <c r="S3">
-        <v>1.39</v>
+        <v>1.24</v>
       </c>
       <c r="T3">
-        <v>2.88</v>
+        <v>3.75</v>
       </c>
       <c r="U3">
-        <v>2.72</v>
+        <v>2.2</v>
       </c>
       <c r="V3">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="W3">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="X3">
         <v>1.01</v>
       </c>
       <c r="Y3">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="Z3">
-        <v>3.08</v>
+        <v>5.37</v>
       </c>
       <c r="AA3">
-        <v>1.92</v>
+        <v>1.5</v>
       </c>
       <c r="AB3">
-        <v>1.76</v>
+        <v>2.38</v>
       </c>
       <c r="AC3">
-        <v>3.28</v>
+        <v>2.13</v>
       </c>
       <c r="AD3">
-        <v>1.25</v>
+        <v>1.61</v>
       </c>
       <c r="AE3">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="AF3">
-        <v>1.76</v>
+        <v>1.48</v>
       </c>
       <c r="AG3">
-        <v>2</v>
+        <v>2.45</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.6</v>
+        <v>1.17</v>
       </c>
       <c r="AK3">
-        <v>1.3</v>
+        <v>1.95</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G4">
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.52</v>
+        <v>2.98</v>
       </c>
       <c r="O4">
-        <v>4</v>
+        <v>3.35</v>
       </c>
       <c r="P4">
-        <v>3.75</v>
+        <v>2.19</v>
       </c>
       <c r="Q4">
-        <v>2.22</v>
+        <v>3.88</v>
       </c>
       <c r="R4">
-        <v>2.21</v>
+        <v>2.17</v>
       </c>
       <c r="S4">
-        <v>1.24</v>
+        <v>1.39</v>
       </c>
       <c r="T4">
-        <v>3.75</v>
+        <v>2.88</v>
       </c>
       <c r="U4">
-        <v>2.2</v>
+        <v>2.72</v>
       </c>
       <c r="V4">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="W4">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="X4">
         <v>1.01</v>
       </c>
       <c r="Y4">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="Z4">
-        <v>5.37</v>
+        <v>3.08</v>
       </c>
       <c r="AA4">
-        <v>1.5</v>
+        <v>1.92</v>
       </c>
       <c r="AB4">
-        <v>2.38</v>
+        <v>1.76</v>
       </c>
       <c r="AC4">
-        <v>2.13</v>
+        <v>3.28</v>
       </c>
       <c r="AD4">
-        <v>1.61</v>
+        <v>1.25</v>
       </c>
       <c r="AE4">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AF4">
-        <v>1.48</v>
+        <v>1.76</v>
       </c>
       <c r="AG4">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.17</v>
+        <v>1.6</v>
       </c>
       <c r="AK4">
-        <v>1.95</v>
+        <v>1.3</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1133,55 +1133,55 @@
         <v>1.66</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="AA5">
         <v>1.65</v>
       </c>
       <c r="AB5">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>JS El Biar</t>
         </is>
       </c>
       <c r="G14">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Temouchent</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>JS El Biar</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G15">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Temouchent</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G16">

--- a/jogos_2026-09-30.xlsx
+++ b/jogos_2026-09-30.xlsx
@@ -798,16 +798,16 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.52</v>
+        <v>1.77</v>
       </c>
       <c r="O3">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="P3">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="Q3">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="R3">
         <v>2.21</v>
@@ -819,10 +819,10 @@
         <v>3.75</v>
       </c>
       <c r="U3">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="V3">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="W3">
         <v>1.15</v>
@@ -837,25 +837,25 @@
         <v>5.37</v>
       </c>
       <c r="AA3">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AB3">
         <v>2.38</v>
       </c>
       <c r="AC3">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="AD3">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AE3">
         <v>1.22</v>
       </c>
       <c r="AF3">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AG3">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
         <v>1.17</v>
       </c>
       <c r="AK3">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,16 +961,16 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="O4">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="P4">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="Q4">
-        <v>3.88</v>
+        <v>3.83</v>
       </c>
       <c r="R4">
         <v>2.17</v>
@@ -1000,10 +1000,10 @@
         <v>3.08</v>
       </c>
       <c r="AA4">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AB4">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AC4">
         <v>3.28</v>
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AK4">
         <v>1.3</v>
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="O6">
+        <v>3.8</v>
+      </c>
+      <c r="P6">
         <v>3.45</v>
-      </c>
-      <c r="P6">
-        <v>3.2</v>
       </c>
       <c r="Q6">
         <v>2.32</v>
@@ -1360,7 +1360,7 @@
         <v>1.2</v>
       </c>
       <c r="AK6">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.99</v>
+        <v>1.91</v>
       </c>
       <c r="O8">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P8">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="Q8">
         <v>2.46</v>
@@ -3083,61 +3083,61 @@
         <v>1.43</v>
       </c>
       <c r="O17">
-        <v>3.72</v>
+        <v>3.63</v>
       </c>
       <c r="P17">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="Q17">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="R17">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S17">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T17">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="U17">
-        <v>2.55</v>
+        <v>2.69</v>
       </c>
       <c r="V17">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="W17">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X17">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y17">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="Z17">
-        <v>3.42</v>
+        <v>3.14</v>
       </c>
       <c r="AA17">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="AB17">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AC17">
-        <v>3.08</v>
+        <v>3.34</v>
       </c>
       <c r="AD17">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AE17">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF17">
-        <v>1.84</v>
+        <v>1.92</v>
       </c>
       <c r="AG17">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AK17">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AL17">
         <v>0</v>

--- a/jogos_2026-09-30.xlsx
+++ b/jogos_2026-09-30.xlsx
@@ -1446,7 +1446,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N7">

--- a/jogos_2026-09-30.xlsx
+++ b/jogos_2026-09-30.xlsx
@@ -644,55 +644,55 @@
         <v>2.11</v>
       </c>
       <c r="Q2">
-        <v>4.05</v>
+        <v>3.75</v>
       </c>
       <c r="R2">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="S2">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="T2">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="U2">
-        <v>2.78</v>
+        <v>2.95</v>
       </c>
       <c r="V2">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W2">
+        <v>1.06</v>
+      </c>
+      <c r="X2">
         <v>1.05</v>
       </c>
-      <c r="X2">
-        <v>1.01</v>
-      </c>
       <c r="Y2">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="Z2">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="AA2">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AB2">
-        <v>1.77</v>
+        <v>1.69</v>
       </c>
       <c r="AC2">
-        <v>3.28</v>
+        <v>3.9</v>
       </c>
       <c r="AD2">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AE2">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF2">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AG2">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK2">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -798,31 +798,31 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.77</v>
+        <v>1.45</v>
       </c>
       <c r="O3">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="P3">
-        <v>3.6</v>
+        <v>4.58</v>
       </c>
       <c r="Q3">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="R3">
-        <v>2.21</v>
+        <v>2.61</v>
       </c>
       <c r="S3">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="T3">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="U3">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="V3">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="W3">
         <v>1.15</v>
@@ -831,25 +831,25 @@
         <v>1.01</v>
       </c>
       <c r="Y3">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="Z3">
-        <v>5.37</v>
+        <v>5.61</v>
       </c>
       <c r="AA3">
         <v>1.46</v>
       </c>
       <c r="AB3">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="AC3">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AD3">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="AE3">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AF3">
         <v>1.47</v>
@@ -871,7 +871,7 @@
         <v>1.17</v>
       </c>
       <c r="AK3">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,16 +961,16 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.99</v>
+        <v>3.15</v>
       </c>
       <c r="O4">
         <v>3.2</v>
       </c>
       <c r="P4">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="Q4">
-        <v>3.83</v>
+        <v>3.98</v>
       </c>
       <c r="R4">
         <v>2.17</v>
@@ -979,10 +979,10 @@
         <v>1.39</v>
       </c>
       <c r="T4">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="U4">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="V4">
         <v>1.36</v>
@@ -994,16 +994,16 @@
         <v>1.01</v>
       </c>
       <c r="Y4">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z4">
-        <v>3.08</v>
+        <v>3.18</v>
       </c>
       <c r="AA4">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="AB4">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AC4">
         <v>3.28</v>
@@ -1018,7 +1018,7 @@
         <v>1.76</v>
       </c>
       <c r="AG4">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AK4">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1124,49 +1124,49 @@
         </is>
       </c>
       <c r="N5">
-        <v>4.25</v>
+        <v>4.1</v>
       </c>
       <c r="O5">
-        <v>3.68</v>
+        <v>4.16</v>
       </c>
       <c r="P5">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="Q5">
-        <v>4.75</v>
+        <v>4.54</v>
       </c>
       <c r="R5">
-        <v>2.22</v>
+        <v>2.44</v>
       </c>
       <c r="S5">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T5">
         <v>2.99</v>
       </c>
       <c r="U5">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="V5">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="W5">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X5">
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="Z5">
-        <v>3.94</v>
+        <v>4.11</v>
       </c>
       <c r="AA5">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AB5">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AC5">
         <v>2.52</v>
@@ -1175,7 +1175,7 @@
         <v>1.41</v>
       </c>
       <c r="AE5">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF5">
         <v>1.61</v>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.19</v>
+        <v>1.89</v>
       </c>
       <c r="AK5">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="O6">
         <v>3.8</v>
       </c>
       <c r="P6">
-        <v>3.45</v>
+        <v>2.95</v>
       </c>
       <c r="Q6">
         <v>2.32</v>
@@ -1305,7 +1305,7 @@
         <v>1.29</v>
       </c>
       <c r="T6">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="U6">
         <v>2.34</v>
@@ -1317,7 +1317,7 @@
         <v>1.13</v>
       </c>
       <c r="X6">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y6">
         <v>1.2</v>
@@ -1332,7 +1332,7 @@
         <v>2.25</v>
       </c>
       <c r="AC6">
-        <v>2.63</v>
+        <v>2.64</v>
       </c>
       <c r="AD6">
         <v>1.4</v>
@@ -1360,7 +1360,7 @@
         <v>1.2</v>
       </c>
       <c r="AK6">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="O8">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P8">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="Q8">
         <v>2.46</v>
@@ -1631,16 +1631,16 @@
         <v>1.3</v>
       </c>
       <c r="T8">
-        <v>3.26</v>
+        <v>3.27</v>
       </c>
       <c r="U8">
-        <v>2.61</v>
+        <v>2.46</v>
       </c>
       <c r="V8">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W8">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X8">
         <v>1.03</v>
@@ -1661,7 +1661,7 @@
         <v>2.81</v>
       </c>
       <c r="AD8">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AE8">
         <v>1.14</v>
@@ -3089,49 +3089,49 @@
         <v>4.8</v>
       </c>
       <c r="Q17">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="R17">
         <v>2.2</v>
       </c>
       <c r="S17">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="T17">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="U17">
-        <v>2.69</v>
+        <v>2.73</v>
       </c>
       <c r="V17">
         <v>1.37</v>
       </c>
       <c r="W17">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y17">
         <v>1.27</v>
       </c>
       <c r="Z17">
-        <v>3.14</v>
+        <v>3.28</v>
       </c>
       <c r="AA17">
         <v>2</v>
       </c>
       <c r="AB17">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="AC17">
-        <v>3.34</v>
+        <v>3.21</v>
       </c>
       <c r="AD17">
         <v>1.24</v>
       </c>
       <c r="AE17">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AF17">
         <v>1.92</v>

--- a/jogos_2026-09-30.xlsx
+++ b/jogos_2026-09-30.xlsx
@@ -653,10 +653,10 @@
         <v>1.41</v>
       </c>
       <c r="T2">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="U2">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="V2">
         <v>1.35</v>
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G3">
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.45</v>
+        <v>3.25</v>
       </c>
       <c r="O3">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="P3">
-        <v>4.58</v>
+        <v>1.95</v>
       </c>
       <c r="Q3">
-        <v>2.22</v>
+        <v>4.12</v>
       </c>
       <c r="R3">
-        <v>2.61</v>
+        <v>2.2</v>
       </c>
       <c r="S3">
-        <v>1.23</v>
+        <v>1.38</v>
       </c>
       <c r="T3">
-        <v>4</v>
+        <v>2.88</v>
       </c>
       <c r="U3">
-        <v>2.18</v>
+        <v>2.67</v>
       </c>
       <c r="V3">
-        <v>1.68</v>
+        <v>1.38</v>
       </c>
       <c r="W3">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="X3">
         <v>1.01</v>
       </c>
       <c r="Y3">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="Z3">
-        <v>5.61</v>
+        <v>3.21</v>
       </c>
       <c r="AA3">
-        <v>1.46</v>
+        <v>1.92</v>
       </c>
       <c r="AB3">
-        <v>2.63</v>
+        <v>1.84</v>
       </c>
       <c r="AC3">
-        <v>2.05</v>
+        <v>3.28</v>
       </c>
       <c r="AD3">
-        <v>1.66</v>
+        <v>1.25</v>
       </c>
       <c r="AE3">
-        <v>1.25</v>
+        <v>1.06</v>
       </c>
       <c r="AF3">
-        <v>1.47</v>
+        <v>1.77</v>
       </c>
       <c r="AG3">
-        <v>2.47</v>
+        <v>1.95</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.17</v>
+        <v>1.68</v>
       </c>
       <c r="AK3">
-        <v>2.05</v>
+        <v>1.22</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="G4">
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>3.15</v>
+        <v>1.63</v>
       </c>
       <c r="O4">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="P4">
-        <v>2.1</v>
+        <v>4.3</v>
       </c>
       <c r="Q4">
-        <v>3.98</v>
+        <v>2.2</v>
       </c>
       <c r="R4">
+        <v>2.72</v>
+      </c>
+      <c r="S4">
+        <v>1.25</v>
+      </c>
+      <c r="T4">
+        <v>4</v>
+      </c>
+      <c r="U4">
         <v>2.17</v>
       </c>
-      <c r="S4">
-        <v>1.39</v>
-      </c>
-      <c r="T4">
-        <v>3</v>
-      </c>
-      <c r="U4">
-        <v>2.68</v>
-      </c>
       <c r="V4">
-        <v>1.36</v>
+        <v>1.68</v>
       </c>
       <c r="W4">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="X4">
         <v>1.01</v>
       </c>
       <c r="Y4">
+        <v>1.1</v>
+      </c>
+      <c r="Z4">
+        <v>5.69</v>
+      </c>
+      <c r="AA4">
+        <v>1.42</v>
+      </c>
+      <c r="AB4">
+        <v>2.49</v>
+      </c>
+      <c r="AC4">
+        <v>2.05</v>
+      </c>
+      <c r="AD4">
+        <v>1.66</v>
+      </c>
+      <c r="AE4">
         <v>1.29</v>
       </c>
-      <c r="Z4">
-        <v>3.18</v>
-      </c>
-      <c r="AA4">
-        <v>1.92</v>
-      </c>
-      <c r="AB4">
-        <v>1.82</v>
-      </c>
-      <c r="AC4">
-        <v>3.28</v>
-      </c>
-      <c r="AD4">
-        <v>1.25</v>
-      </c>
-      <c r="AE4">
-        <v>1.1</v>
-      </c>
       <c r="AF4">
-        <v>1.76</v>
+        <v>1.47</v>
       </c>
       <c r="AG4">
-        <v>2.1</v>
+        <v>2.47</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.62</v>
+        <v>1.17</v>
       </c>
       <c r="AK4">
-        <v>1.25</v>
+        <v>2.05</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1127,10 +1127,10 @@
         <v>4.1</v>
       </c>
       <c r="O5">
-        <v>4.16</v>
+        <v>3.7</v>
       </c>
       <c r="P5">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="Q5">
         <v>4.54</v>
@@ -1139,10 +1139,10 @@
         <v>2.44</v>
       </c>
       <c r="S5">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T5">
-        <v>2.99</v>
+        <v>3.05</v>
       </c>
       <c r="U5">
         <v>2.39</v>
@@ -1157,16 +1157,16 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="Z5">
-        <v>4.11</v>
+        <v>3.98</v>
       </c>
       <c r="AA5">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AB5">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AC5">
         <v>2.52</v>
@@ -1178,10 +1178,10 @@
         <v>1.15</v>
       </c>
       <c r="AF5">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AG5">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1287,16 +1287,16 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="O6">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="P6">
-        <v>2.95</v>
+        <v>3.4</v>
       </c>
       <c r="Q6">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="R6">
         <v>2.3</v>
@@ -1320,25 +1320,25 @@
         <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="Z6">
-        <v>4.25</v>
+        <v>4.1</v>
       </c>
       <c r="AA6">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AB6">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AC6">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="AD6">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AE6">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AF6">
         <v>1.57</v>
@@ -1357,7 +1357,7 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK6">
         <v>1.82</v>
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O7">
+        <v>3.83</v>
+      </c>
+      <c r="P7">
+        <v>1.95</v>
+      </c>
+      <c r="Q7">
+        <v>3.34</v>
+      </c>
+      <c r="R7">
+        <v>2.5</v>
+      </c>
+      <c r="S7">
+        <v>1.2</v>
+      </c>
+      <c r="T7">
         <v>4</v>
       </c>
-      <c r="P7">
-        <v>1.85</v>
-      </c>
-      <c r="Q7">
-        <v>3.24</v>
-      </c>
-      <c r="R7">
-        <v>2.6</v>
-      </c>
-      <c r="S7">
-        <v>1.17</v>
-      </c>
-      <c r="T7">
-        <v>4.2</v>
-      </c>
       <c r="U7">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="V7">
         <v>1.77</v>
       </c>
       <c r="W7">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X7">
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Z7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA7">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AB7">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AC7">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AD7">
-        <v>1.87</v>
+        <v>1.73</v>
       </c>
       <c r="AE7">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AF7">
         <v>1.4</v>
       </c>
       <c r="AG7">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>1.22</v>
       </c>
       <c r="AK7">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1616,16 +1616,16 @@
         <v>1.9</v>
       </c>
       <c r="O8">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="P8">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="Q8">
-        <v>2.46</v>
+        <v>2.54</v>
       </c>
       <c r="R8">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="S8">
         <v>1.3</v>
@@ -1634,10 +1634,10 @@
         <v>3.27</v>
       </c>
       <c r="U8">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="V8">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="W8">
         <v>1.08</v>
@@ -1646,19 +1646,19 @@
         <v>1.03</v>
       </c>
       <c r="Y8">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z8">
-        <v>3.82</v>
+        <v>3.8</v>
       </c>
       <c r="AA8">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AB8">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AC8">
-        <v>2.81</v>
+        <v>2.96</v>
       </c>
       <c r="AD8">
         <v>1.39</v>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK8">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.43</v>
+        <v>1.62</v>
       </c>
       <c r="O17">
         <v>3.63</v>
       </c>
       <c r="P17">
-        <v>4.8</v>
+        <v>4.88</v>
       </c>
       <c r="Q17">
         <v>2.05</v>
@@ -3107,7 +3107,7 @@
         <v>1.37</v>
       </c>
       <c r="W17">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X17">
         <v>1.03</v>
@@ -3119,7 +3119,7 @@
         <v>3.28</v>
       </c>
       <c r="AA17">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AB17">
         <v>1.86</v>
@@ -3134,10 +3134,10 @@
         <v>1.07</v>
       </c>
       <c r="AF17">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AG17">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>

--- a/jogos_2026-09-30.xlsx
+++ b/jogos_2026-09-30.xlsx
@@ -644,43 +644,43 @@
         <v>2.11</v>
       </c>
       <c r="Q2">
-        <v>3.75</v>
+        <v>4.33</v>
       </c>
       <c r="R2">
         <v>2.05</v>
       </c>
       <c r="S2">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="T2">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="U2">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="V2">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W2">
         <v>1.06</v>
       </c>
       <c r="X2">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y2">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z2">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="AA2">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AB2">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="AC2">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="AD2">
         <v>1.3</v>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AK2">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -798,31 +798,31 @@
         </is>
       </c>
       <c r="N3">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="O3">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P3">
-        <v>1.95</v>
+        <v>1.84</v>
       </c>
       <c r="Q3">
-        <v>4.12</v>
+        <v>4.58</v>
       </c>
       <c r="R3">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S3">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="T3">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="U3">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="V3">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W3">
         <v>1.05</v>
@@ -834,13 +834,13 @@
         <v>1.3</v>
       </c>
       <c r="Z3">
-        <v>3.21</v>
+        <v>3.19</v>
       </c>
       <c r="AA3">
         <v>1.92</v>
       </c>
       <c r="AB3">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AC3">
         <v>3.28</v>
@@ -852,10 +852,10 @@
         <v>1.06</v>
       </c>
       <c r="AF3">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="AG3">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.68</v>
+        <v>1.81</v>
       </c>
       <c r="AK3">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -970,55 +970,55 @@
         <v>4.3</v>
       </c>
       <c r="Q4">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="R4">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="S4">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="T4">
         <v>4</v>
       </c>
       <c r="U4">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="V4">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="W4">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="X4">
         <v>1.01</v>
       </c>
       <c r="Y4">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Z4">
-        <v>5.69</v>
+        <v>5.3</v>
       </c>
       <c r="AA4">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AB4">
-        <v>2.49</v>
+        <v>2.52</v>
       </c>
       <c r="AC4">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AD4">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AE4">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AF4">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="AG4">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>1.17</v>
       </c>
       <c r="AK4">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>4.1</v>
+        <v>4.62</v>
       </c>
       <c r="O5">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="P5">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="Q5">
-        <v>4.54</v>
+        <v>5</v>
       </c>
       <c r="R5">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="S5">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T5">
-        <v>3.05</v>
+        <v>3.61</v>
       </c>
       <c r="U5">
-        <v>2.39</v>
+        <v>2.18</v>
       </c>
       <c r="V5">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="W5">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X5">
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="Z5">
-        <v>3.98</v>
+        <v>4.85</v>
       </c>
       <c r="AA5">
-        <v>1.63</v>
+        <v>1.45</v>
       </c>
       <c r="AB5">
-        <v>2.1</v>
+        <v>2.41</v>
       </c>
       <c r="AC5">
-        <v>2.52</v>
+        <v>2.17</v>
       </c>
       <c r="AD5">
-        <v>1.41</v>
+        <v>1.59</v>
       </c>
       <c r="AE5">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AF5">
-        <v>1.6</v>
+        <v>1.51</v>
       </c>
       <c r="AG5">
-        <v>2.11</v>
+        <v>2.29</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.89</v>
+        <v>2.09</v>
       </c>
       <c r="AK5">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1296,7 +1296,7 @@
         <v>3.4</v>
       </c>
       <c r="Q6">
-        <v>2.31</v>
+        <v>2.27</v>
       </c>
       <c r="R6">
         <v>2.3</v>
@@ -1308,10 +1308,10 @@
         <v>3.25</v>
       </c>
       <c r="U6">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="V6">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="W6">
         <v>1.13</v>
@@ -1320,28 +1320,28 @@
         <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z6">
-        <v>4.1</v>
+        <v>4.22</v>
       </c>
       <c r="AA6">
         <v>1.6</v>
       </c>
       <c r="AB6">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AC6">
-        <v>2.67</v>
+        <v>2.66</v>
       </c>
       <c r="AD6">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="AE6">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AF6">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AG6">
         <v>2.25</v>
@@ -1360,7 +1360,7 @@
         <v>1.18</v>
       </c>
       <c r="AK6">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1616,16 +1616,16 @@
         <v>1.9</v>
       </c>
       <c r="O8">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="P8">
         <v>3.25</v>
       </c>
       <c r="Q8">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="R8">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="S8">
         <v>1.3</v>
@@ -1634,7 +1634,7 @@
         <v>3.27</v>
       </c>
       <c r="U8">
-        <v>2.47</v>
+        <v>2.49</v>
       </c>
       <c r="V8">
         <v>1.52</v>
@@ -1649,28 +1649,28 @@
         <v>1.19</v>
       </c>
       <c r="Z8">
-        <v>3.8</v>
+        <v>3.74</v>
       </c>
       <c r="AA8">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="AB8">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="AC8">
-        <v>2.96</v>
+        <v>3.01</v>
       </c>
       <c r="AD8">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AE8">
         <v>1.14</v>
       </c>
       <c r="AF8">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AG8">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -3083,61 +3083,61 @@
         <v>1.62</v>
       </c>
       <c r="O17">
-        <v>3.63</v>
+        <v>3.4</v>
       </c>
       <c r="P17">
-        <v>4.88</v>
+        <v>4.3</v>
       </c>
       <c r="Q17">
-        <v>2.05</v>
+        <v>2.17</v>
       </c>
       <c r="R17">
         <v>2.2</v>
       </c>
       <c r="S17">
+        <v>1.38</v>
+      </c>
+      <c r="T17">
+        <v>2.89</v>
+      </c>
+      <c r="U17">
+        <v>2.66</v>
+      </c>
+      <c r="V17">
         <v>1.4</v>
       </c>
-      <c r="T17">
-        <v>2.82</v>
-      </c>
-      <c r="U17">
-        <v>2.73</v>
-      </c>
-      <c r="V17">
-        <v>1.37</v>
-      </c>
       <c r="W17">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X17">
         <v>1.03</v>
       </c>
       <c r="Y17">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="Z17">
-        <v>3.28</v>
+        <v>3.51</v>
       </c>
       <c r="AA17">
         <v>1.95</v>
       </c>
       <c r="AB17">
+        <v>1.94</v>
+      </c>
+      <c r="AC17">
+        <v>2.99</v>
+      </c>
+      <c r="AD17">
+        <v>1.27</v>
+      </c>
+      <c r="AE17">
+        <v>1.09</v>
+      </c>
+      <c r="AF17">
         <v>1.86</v>
       </c>
-      <c r="AC17">
-        <v>3.21</v>
-      </c>
-      <c r="AD17">
-        <v>1.24</v>
-      </c>
-      <c r="AE17">
-        <v>1.07</v>
-      </c>
-      <c r="AF17">
-        <v>1.91</v>
-      </c>
       <c r="AG17">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>1.09</v>
       </c>
       <c r="AK17">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="AL17">
         <v>0</v>
